--- a/Waiting_List.xlsx
+++ b/Waiting_List.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G9"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -528,19 +528,19 @@
         <v>3</v>
       </c>
       <c r="B6" t="str">
-        <v>Ananthakrishnan M</v>
+        <v>SAMSON S SEEMON</v>
       </c>
       <c r="C6" t="str">
-        <v>2327</v>
+        <v>1773</v>
       </c>
       <c r="D6" t="str">
         <v>Insufficient Exp</v>
       </c>
       <c r="E6" t="str">
-        <v>ananthakrishnan0612@gmail.com</v>
+        <v>samson53538@gmail.com</v>
       </c>
       <c r="F6" t="str">
-        <v>9497053327</v>
+        <v>8075019741</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -551,19 +551,19 @@
         <v>4</v>
       </c>
       <c r="B7" t="str">
-        <v>Athul Krishnan A S</v>
+        <v>Ananthakrishnan M</v>
       </c>
       <c r="C7" t="str">
-        <v>3296</v>
+        <v>2327</v>
       </c>
       <c r="D7" t="str">
-        <v>Seats Full</v>
+        <v>Insufficient Exp</v>
       </c>
       <c r="E7" t="str">
-        <v>athulkrishnanas321@gmail.com</v>
+        <v>ananthakrishnan0612@gmail.com</v>
       </c>
       <c r="F7" t="str">
-        <v>8078114005</v>
+        <v>9497053327</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -574,19 +574,19 @@
         <v>5</v>
       </c>
       <c r="B8" t="str">
-        <v>Ganesh A</v>
+        <v>Jijo George</v>
       </c>
       <c r="C8" t="str">
-        <v>3601</v>
+        <v>4052</v>
       </c>
       <c r="D8" t="str">
-        <v>Seats Full</v>
+        <v>Insufficient Exp</v>
       </c>
       <c r="E8" t="str">
-        <v>ganeshkumar10170@gmail.com</v>
+        <v>jijog4629@gmail.com</v>
       </c>
       <c r="F8" t="str">
-        <v>6282562207</v>
+        <v>9072911806</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -597,67 +597,21 @@
         <v>6</v>
       </c>
       <c r="B9" t="str">
-        <v>Jijo George</v>
+        <v>KANNANUNNI G S</v>
       </c>
       <c r="C9" t="str">
-        <v>4052</v>
+        <v>4</v>
       </c>
       <c r="D9" t="str">
         <v>Insufficient Exp</v>
       </c>
       <c r="E9" t="str">
-        <v>jijog4629@gmail.com</v>
+        <v>kannanunni062@gmail.com</v>
       </c>
       <c r="F9" t="str">
-        <v>9072911806</v>
+        <v>9567018318</v>
       </c>
       <c r="G9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>7</v>
-      </c>
-      <c r="B10" t="str">
-        <v>AMAL M</v>
-      </c>
-      <c r="C10" t="str">
-        <v>4553</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Seats Full</v>
-      </c>
-      <c r="E10" t="str">
-        <v>amalmahesh42@gmail.com</v>
-      </c>
-      <c r="F10" t="str">
-        <v>7902318852</v>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>8</v>
-      </c>
-      <c r="B11" t="str">
-        <v>KANNANUNNI G S</v>
-      </c>
-      <c r="C11" t="str">
-        <v>4</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Insufficient Exp</v>
-      </c>
-      <c r="E11" t="str">
-        <v>kannanunni062@gmail.com</v>
-      </c>
-      <c r="F11" t="str">
-        <v>9567018318</v>
-      </c>
-      <c r="G11" t="str">
         <v/>
       </c>
     </row>
@@ -667,7 +621,7 @@
     <mergeCell ref="A2:G2"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G9"/>
   </ignoredErrors>
 </worksheet>
 </file>